--- a/sequences/retrieval_blockB_fixed-middle-10_13.xlsx
+++ b/sequences/retrieval_blockB_fixed-middle-10_13.xlsx
@@ -491,32 +491,32 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>is_yes</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>distance_correct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>type2_anchor_pos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dist_anchor_to_foil</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>image_dur_retr</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fix_dur_retr</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>is_yes</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -557,27 +557,23 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -591,36 +587,32 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>9</v>
-      </c>
       <c r="U2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -640,54 +632,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
         <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>10</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -695,7 +673,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -715,70 +693,62 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_34.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
         <v>4</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.2</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -798,48 +768,70 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>stimuli/flower/flower_20.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_20.jpg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -864,18 +856,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_34.jpg</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -888,33 +884,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -934,27 +934,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -970,34 +966,30 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.2</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1017,65 +1009,57 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.2</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1100,12 +1084,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1114,26 +1098,26 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.5</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1141,7 +1125,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1161,23 +1145,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1190,33 +1178,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>3</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Q10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.2</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1236,23 +1228,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_17.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_30.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1265,28 +1261,32 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P11" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.2</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
       <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
         <v>9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>10</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1341,24 +1341,24 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>0.2</v>
       </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1407,33 +1407,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>0.2</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1475,26 +1475,26 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.5</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1522,14 +1522,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_22.jpg</t>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1555,29 +1555,29 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
       </c>
       <c r="P15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>0.2</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="n">
         <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>9</v>
       </c>
       <c r="U15" t="n">
         <v>1</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1638,37 +1638,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S16" t="n">
         <v>8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>10</v>
       </c>
       <c r="T16" t="n">
         <v>9</v>
       </c>
       <c r="U16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1688,70 +1688,62 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>6</v>
-      </c>
       <c r="T17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1771,54 +1763,40 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1846,12 +1824,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1867,33 +1845,33 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>0.2</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1901,7 +1879,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1921,43 +1899,65 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2015,37 +2015,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S21" t="n">
         <v>4</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>8</v>
       </c>
       <c r="T21" t="n">
         <v>5</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2073,40 +2073,62 @@
           <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R22" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="n">
         <v>10</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2126,27 +2148,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2160,31 +2178,27 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.2</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2209,27 +2223,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2242,32 +2256,32 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>2</v>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
       </c>
       <c r="P24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>0.2</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -2292,12 +2306,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2313,33 +2327,33 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>0.2</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2347,7 +2361,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2367,7 +2381,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2376,42 +2390,28 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2442,54 +2442,40 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2497,7 +2483,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2517,70 +2503,62 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_17.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/dog/dog_03.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S28" t="n">
         <v>4</v>
       </c>
-      <c r="P28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>6</v>
-      </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2600,48 +2578,70 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_30.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R29" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2661,27 +2661,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
           <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2695,36 +2691,32 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>7</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.2</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2744,62 +2736,70 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_18.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P31" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.2</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
       <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="n">
         <v>5</v>
       </c>
-      <c r="T31" t="n">
-        <v>7</v>
-      </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2827,54 +2827,62 @@
           <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P32" t="n">
-        <v>1.2</v>
+        <v>6</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.2</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T32" t="n">
         <v>6</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2894,70 +2902,62 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_20.jpg</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>2</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.2</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2977,40 +2977,54 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R34" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3018,7 +3032,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3038,62 +3052,70 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_34.jpg</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P35" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.2</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3113,70 +3135,48 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
           <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_13.jpg</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
         <v>4</v>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>8</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R36" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3196,70 +3196,48 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.5</v>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R37" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3279,27 +3257,23 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/ball/ball_17.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3313,36 +3287,32 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.2</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3362,40 +3332,54 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>4</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R39" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3403,7 +3387,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3423,23 +3407,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3452,33 +3440,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P40" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R40" t="n">
         <v>0.2</v>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
         <v>6</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3503,18 +3495,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3527,33 +3523,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P41" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R41" t="n">
         <v>0.2</v>
       </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
       <c r="S41" t="n">
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3573,65 +3573,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.5</v>
+      </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3656,27 +3634,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3689,37 +3667,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M43" t="n">
-        <v>3</v>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="inlineStr">
         <is>
           <t>inside</t>
         </is>
       </c>
-      <c r="O43" t="n">
-        <v>4</v>
-      </c>
       <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>0.2</v>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3739,40 +3717,54 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="n">
-        <v>2</v>
-      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R44" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -3800,12 +3792,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3830,24 +3822,24 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>4</v>
+      </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="n">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>0.2</v>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -3855,7 +3847,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3875,23 +3867,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3904,33 +3900,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M46" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>3</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P46" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R46" t="n">
         <v>0.2</v>
       </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
       <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="n">
         <v>8</v>
       </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3958,62 +3958,54 @@
           <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.2</v>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4033,62 +4025,70 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
-        <v>4</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>2</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P48" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R48" t="n">
         <v>0.2</v>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4116,62 +4116,54 @@
           <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_17.jpg</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>7</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R49" t="n">
         <v>0.2</v>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4191,23 +4183,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_03.jpg</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4220,28 +4216,32 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M50" t="n">
-        <v>2</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P50" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R50" t="n">
         <v>0.2</v>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -4280,26 +4280,26 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>4</v>
+      </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>2</v>
-      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
         <v>0.5</v>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4327,27 +4327,23 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
           <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4361,36 +4357,32 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R52" t="n">
         <v>0.2</v>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4410,57 +4402,65 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P53" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R53" t="n">
         <v>0.2</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
@@ -4485,12 +4485,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4499,26 +4499,26 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M54" t="n">
-        <v>4</v>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>2</v>
+      </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>2</v>
-      </c>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="n">
+        <v>2</v>
+      </c>
+      <c r="R54" t="n">
         <v>0.5</v>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4546,23 +4546,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>stimuli/bread/bread_34.jpg</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4575,33 +4579,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M55" t="n">
-        <v>2</v>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
       <c r="P55" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R55" t="n">
         <v>0.2</v>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4621,27 +4629,23 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/flower/flower_20.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4655,36 +4659,32 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>7</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R56" t="n">
         <v>0.2</v>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T56" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4704,54 +4704,40 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>4</v>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -4759,7 +4745,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4779,27 +4765,23 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_17.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4815,29 +4797,25 @@
       <c r="M58" t="n">
         <v>1</v>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="O58" t="n">
-        <v>2</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="N58" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R58" t="n">
         <v>0.2</v>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4862,27 +4840,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_17.jpg</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4895,37 +4873,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M59" t="n">
-        <v>2</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="O59" t="n">
-        <v>3</v>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
       </c>
       <c r="P59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q59" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>0.2</v>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -4945,40 +4923,54 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>2</v>
-      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R60" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -4986,7 +4978,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5006,57 +4998,65 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
-        <v>3</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>4</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
       <c r="P61" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="Q61" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R61" t="n">
         <v>0.2</v>
       </c>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/sequences/retrieval_blockB_fixed-middle-10_13.xlsx
+++ b/sequences/retrieval_blockB_fixed-middle-10_13.xlsx
@@ -491,32 +491,32 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>distance_correct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>type2_anchor_pos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dist_anchor_to_foil</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>image_dur_retr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fix_dur_retr</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>is_yes</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>distance_correct</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>type2_anchor_pos</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dist_anchor_to_foil</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>image_dur_retr</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>fix_dur_retr</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -557,62 +557,70 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R2" t="n">
         <v>0.2</v>
       </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U2" t="n">
         <v>4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -632,40 +640,54 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -673,7 +695,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -693,54 +715,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -748,7 +756,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -773,60 +781,52 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -851,27 +851,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -884,32 +884,32 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
       <c r="P6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
-      </c>
       <c r="U6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -939,7 +939,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -964,24 +964,24 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q7" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1017,54 +1017,62 @@
           <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R8" t="n">
         <v>0.2</v>
       </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1084,40 +1092,54 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1125,7 +1147,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1145,65 +1167,43 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_32.jpg</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_32.jpg</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>3</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1228,29 +1228,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>left</t>
@@ -1261,37 +1261,37 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R11" t="n">
         <v>0.2</v>
       </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
         <v>6</v>
-      </c>
-      <c r="U11" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1311,23 +1311,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_13.jpg</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1341,27 +1345,31 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R12" t="n">
         <v>0.2</v>
       </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1386,12 +1394,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1407,33 +1415,33 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q13" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
         <v>5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1441,7 +1449,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1461,40 +1469,54 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_31.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1502,7 +1524,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1522,65 +1544,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_22.jpg</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1605,14 +1605,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_34.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_31.jpg</t>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1638,29 +1638,29 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
+      <c r="M16" t="n">
+        <v>4</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R16" t="n">
         <v>0.2</v>
       </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
         <v>8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>9</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1688,23 +1688,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_03.jpg</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1718,32 +1722,36 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R17" t="n">
         <v>0.2</v>
       </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1763,48 +1771,70 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_18.jpg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_18.jpg</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1824,54 +1854,40 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
       <c r="Q19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1879,7 +1895,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1899,27 +1915,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1932,37 +1944,33 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="n">
-        <v>8</v>
-      </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1982,27 +1990,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2015,32 +2019,28 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2090,37 +2090,37 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>4</v>
-      </c>
-      <c r="O22" t="inlineStr">
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
       <c r="P22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
         <v>5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>10</v>
       </c>
       <c r="U22" t="n">
         <v>4</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2169,30 +2169,30 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q23" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2228,60 +2228,38 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2306,12 +2284,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2338,22 +2316,22 @@
       <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>3</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q25" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="n">
         <v>5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>7</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2361,7 +2339,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2381,43 +2359,65 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_20.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_13.jpg</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="n">
         <v>8</v>
       </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -2459,23 +2459,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
       <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
         <v>0.5</v>
       </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -2533,24 +2533,24 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q28" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2578,65 +2578,65 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
         <v>4</v>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O29" t="n">
+        <v>6</v>
+      </c>
       <c r="P29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>5</v>
       </c>
-      <c r="Q29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>6</v>
-      </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -2691,24 +2691,24 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q30" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2769,37 +2769,37 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R31" t="n">
         <v>0.2</v>
       </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
         <v>5</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2819,70 +2819,48 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
           <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_20.jpg</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2902,62 +2880,70 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_34.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_34.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R33" t="n">
         <v>0.2</v>
       </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>10</v>
+      </c>
+      <c r="U33" t="n">
         <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2982,18 +2968,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>stimuli/ball/ball_22.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3009,30 +2999,34 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R34" t="n">
         <v>0.2</v>
       </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
         <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3057,22 +3051,18 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_34.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3085,37 +3075,33 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>8</v>
       </c>
       <c r="T35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3135,40 +3121,54 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>4</v>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3196,40 +3196,54 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
-        <v>2</v>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3262,7 +3276,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -3289,22 +3303,22 @@
       <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N38" t="n">
-        <v>4</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q38" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3312,7 +3326,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3337,18 +3351,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_17.jpg</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3362,27 +3380,31 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R39" t="n">
         <v>0.2</v>
       </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
         <v>10</v>
       </c>
       <c r="T39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3407,70 +3429,70 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_35.jpg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_30.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr">
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R40" t="n">
         <v>0.2</v>
       </c>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
         <v>5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3</v>
-      </c>
-      <c r="U40" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3495,60 +3517,38 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
-        <v>3</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>2</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" t="n">
         <v>4</v>
       </c>
-      <c r="Q41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>8</v>
-      </c>
       <c r="U41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -3590,23 +3590,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
       <c r="Q42" t="n">
-        <v>2</v>
-      </c>
-      <c r="R42" t="n">
         <v>0.5</v>
       </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3639,65 +3639,65 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/flower/flower_20.jpg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
-        <v>2</v>
-      </c>
-      <c r="O43" t="inlineStr">
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>inside</t>
         </is>
       </c>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R43" t="n">
         <v>0.2</v>
       </c>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
         <v>5</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3717,57 +3717,65 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/jacket/jacket_39.jpg</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R44" t="n">
         <v>0.2</v>
       </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
@@ -3797,7 +3805,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/hand/hand_13.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -3813,33 +3821,33 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>4</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q45" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R45" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -3847,7 +3855,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3867,70 +3875,62 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_22.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_22.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>3</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3950,54 +3950,40 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
       <c r="Q47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4005,7 +3991,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4025,70 +4011,62 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_27.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>2</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U48" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4108,62 +4086,70 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/bicycle/bicycle_09.jpg</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R49" t="n">
         <v>0.2</v>
       </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4183,27 +4169,23 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/house/house_27.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_03.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/chair/chair_32.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4216,37 +4198,33 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
+      <c r="M50" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4266,43 +4244,65 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_32.jpg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_27.jpg</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="n">
-        <v>4</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/chair/chair_06.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_34.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -4348,33 +4348,33 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q52" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R52" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4402,27 +4402,23 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_28.jpg</t>
+          <t>stimuli/bread/bread_34.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
-        </is>
-      </c>
+          <t>stimuli/flower/flower_20.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_06.jpg</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4435,37 +4431,33 @@
           <t>left</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="n">
-        <v>4</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U53" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4485,48 +4477,70 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_13.jpg</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_07.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_06.jpg</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>4</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>5</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q54" t="n">
-        <v>2</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -4546,70 +4560,48 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_39.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_31.jpg</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_34.jpg</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_22.jpg</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_34.jpg</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_22.jpg</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -4629,62 +4621,70 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_39.jpg</t>
+          <t>stimuli/ball/ball_22.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_20.jpg</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>stimuli/house/house_07.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_07.jpg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q56" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R56" t="n">
         <v>0.2</v>
       </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -4704,40 +4704,54 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_09.jpg</t>
+          <t>stimuli/dog/dog_03.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_01.jpg</t>
+          <t>stimuli/ball/ball_17.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="R57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -4745,7 +4759,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -4765,7 +4779,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4773,49 +4787,57 @@
           <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_01.jpg</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>stimuli/hand/hand_01.jpg</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>2</v>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>outside</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>5</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q58" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R58" t="n">
         <v>0.2</v>
       </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T58" t="n">
         <v>9</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -4840,29 +4862,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_18.jpg</t>
+          <t>stimuli/hammer/hammer_13.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_03.jpg</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_03.jpg</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_32.jpg</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_13.jpg</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>right</t>
@@ -4873,32 +4895,32 @@
           <t>right</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>outside</t>
         </is>
       </c>
+      <c r="O59" t="n">
+        <v>5</v>
+      </c>
       <c r="P59" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R59" t="n">
         <v>0.2</v>
       </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
         <v>4</v>
-      </c>
-      <c r="U59" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -4923,12 +4945,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_18.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_03.jpg</t>
+          <t>stimuli/bread/bread_35.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -4953,24 +4975,24 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>1.2</v>
+      </c>
       <c r="Q60" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -4978,7 +5000,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -4998,65 +5020,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_17.jpg</t>
+          <t>stimuli/house/house_27.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_32.jpg</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_35.jpg</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_32.jpg</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>right</t>
-        </is>
-      </c>
+          <t>stimuli/hammer/hammer_13.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>right</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="n">
-        <v>4</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>outside</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.2</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
